--- a/RISULTATI DECOUPLED/RISULTATI_decoupledVitBDGfFe.xlsx
+++ b/RISULTATI DECOUPLED/RISULTATI_decoupledVitBDGfFe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - Politecnico di Milano\Documenti\POLIMI\Tesi\distillation\RISULTATI DECOUPLED\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459EE588-4AEE-4D9E-AB8F-6D25D49F9444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF258492-A441-432B-85C2-5C3948284990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8610" yWindow="-15360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -174,7 +174,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -771,7 +770,7 @@
       <c r="S2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="10" t="s">
+      <c r="Y2" s="9" t="s">
         <v>15</v>
       </c>
       <c r="AF2" t="s">
@@ -817,13 +816,13 @@
       <c r="V4" t="s">
         <v>2</v>
       </c>
-      <c r="AE4" s="9" t="s">
+      <c r="AE4" t="s">
         <v>0</v>
       </c>
-      <c r="AF4" s="9" t="s">
+      <c r="AF4" t="s">
         <v>1</v>
       </c>
-      <c r="AG4" s="9" t="s">
+      <c r="AG4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -873,22 +872,22 @@
       <c r="V5">
         <v>0.91780141282197003</v>
       </c>
-      <c r="AA5" s="9" t="s">
+      <c r="AA5" t="s">
         <v>0</v>
       </c>
-      <c r="AB5" s="9" t="s">
+      <c r="AB5" t="s">
         <v>1</v>
       </c>
-      <c r="AC5" s="9" t="s">
+      <c r="AC5" t="s">
         <v>2</v>
       </c>
-      <c r="AE5" s="9">
+      <c r="AE5">
         <v>534.36255455016999</v>
       </c>
-      <c r="AF5" s="9">
+      <c r="AF5">
         <v>0</v>
       </c>
-      <c r="AG5" s="9">
+      <c r="AG5">
         <v>0.86106818945246999</v>
       </c>
     </row>
@@ -938,22 +937,22 @@
       <c r="V6">
         <v>0.91729487301824997</v>
       </c>
-      <c r="AA6" s="9">
+      <c r="AA6">
         <v>3111.8130683898999</v>
       </c>
-      <c r="AB6" s="9">
+      <c r="AB6">
         <v>0</v>
       </c>
-      <c r="AC6" s="9">
+      <c r="AC6">
         <v>0.84493653842701</v>
       </c>
-      <c r="AE6" s="9">
+      <c r="AE6">
         <v>101.4187335968</v>
       </c>
-      <c r="AF6" s="9">
+      <c r="AF6">
         <v>1</v>
       </c>
-      <c r="AG6" s="9">
+      <c r="AG6">
         <v>0.85637888311796995</v>
       </c>
     </row>
@@ -1003,22 +1002,22 @@
       <c r="V7">
         <v>0.92838062030762003</v>
       </c>
-      <c r="AA7" s="9">
+      <c r="AA7">
         <v>2557.5487613678001</v>
       </c>
-      <c r="AB7" s="9">
+      <c r="AB7">
         <v>1</v>
       </c>
-      <c r="AC7" s="9">
+      <c r="AC7">
         <v>0.83988413611139001</v>
       </c>
-      <c r="AE7" s="9">
+      <c r="AE7">
         <v>101.74632072449</v>
       </c>
-      <c r="AF7" s="9">
+      <c r="AF7">
         <v>2</v>
       </c>
-      <c r="AG7" s="9">
+      <c r="AG7">
         <v>0.83995236512684002</v>
       </c>
     </row>
@@ -1068,22 +1067,22 @@
       <c r="V8">
         <v>0.92154698822556003</v>
       </c>
-      <c r="AA8" s="9">
+      <c r="AA8">
         <v>2530.8189392089998</v>
       </c>
-      <c r="AB8" s="9">
+      <c r="AB8">
         <v>2</v>
       </c>
-      <c r="AC8" s="9">
+      <c r="AC8">
         <v>0.81561513278965003</v>
       </c>
-      <c r="AE8" s="9">
+      <c r="AE8">
         <v>102.06866264343</v>
       </c>
-      <c r="AF8" s="9">
+      <c r="AF8">
         <v>3</v>
       </c>
-      <c r="AG8" s="9">
+      <c r="AG8">
         <v>0.86458724338059001</v>
       </c>
     </row>
@@ -1133,22 +1132,22 @@
       <c r="V9">
         <v>0.94142830510279996</v>
       </c>
-      <c r="AA9" s="9">
+      <c r="AA9">
         <v>2660.9010696411001</v>
       </c>
-      <c r="AB9" s="9">
+      <c r="AB9">
         <v>3</v>
       </c>
-      <c r="AC9" s="9">
+      <c r="AC9">
         <v>0.83852094086127005</v>
       </c>
-      <c r="AE9" s="9">
+      <c r="AE9">
         <v>101.53555870056</v>
       </c>
-      <c r="AF9" s="9">
+      <c r="AF9">
         <v>4</v>
       </c>
-      <c r="AG9" s="9">
+      <c r="AG9">
         <v>0.82773536670587999</v>
       </c>
     </row>
@@ -1198,22 +1197,22 @@
       <c r="V10">
         <v>0.89411425274091005</v>
       </c>
-      <c r="AA10" s="9">
+      <c r="AA10">
         <v>2864.8703098297001</v>
       </c>
-      <c r="AB10" s="9">
+      <c r="AB10">
         <v>4</v>
       </c>
-      <c r="AC10" s="9">
+      <c r="AC10">
         <v>0.87226410505837004</v>
       </c>
-      <c r="AE10" s="9">
+      <c r="AE10">
         <v>101.56059265137</v>
       </c>
-      <c r="AF10" s="9">
+      <c r="AF10">
         <v>5</v>
       </c>
-      <c r="AG10" s="9">
+      <c r="AG10">
         <v>0.86253372811365003</v>
       </c>
     </row>
@@ -1263,22 +1262,22 @@
       <c r="V11">
         <v>0.92310475583986995</v>
       </c>
-      <c r="AA11" s="9">
+      <c r="AA11">
         <v>2667.6390171050998</v>
       </c>
-      <c r="AB11" s="9">
+      <c r="AB11">
         <v>5</v>
       </c>
-      <c r="AC11" s="9">
+      <c r="AC11">
         <v>0.85905547194304999</v>
       </c>
-      <c r="AE11" s="9">
+      <c r="AE11">
         <v>101.59206390381</v>
       </c>
-      <c r="AF11" s="9">
+      <c r="AF11">
         <v>6</v>
       </c>
-      <c r="AG11" s="9">
+      <c r="AG11">
         <v>0.84906534325889005</v>
       </c>
     </row>
@@ -1328,22 +1327,22 @@
       <c r="V12">
         <v>0.91489639193843997</v>
       </c>
-      <c r="AA12" s="9">
+      <c r="AA12">
         <v>2603.5189628601001</v>
       </c>
-      <c r="AB12" s="9">
+      <c r="AB12">
         <v>6</v>
       </c>
-      <c r="AC12" s="9">
+      <c r="AC12">
         <v>0.85991997642716</v>
       </c>
-      <c r="AE12" s="9">
+      <c r="AE12">
         <v>102.22101211547999</v>
       </c>
-      <c r="AF12" s="9">
+      <c r="AF12">
         <v>7</v>
       </c>
-      <c r="AG12" s="9">
+      <c r="AG12">
         <v>0.86080124896129995</v>
       </c>
     </row>
@@ -1393,22 +1392,22 @@
       <c r="V13">
         <v>0.90897005951841003</v>
       </c>
-      <c r="AA13" s="9">
+      <c r="AA13">
         <v>2563.6548995971998</v>
       </c>
-      <c r="AB13" s="9">
+      <c r="AB13">
         <v>7</v>
       </c>
-      <c r="AC13" s="9">
+      <c r="AC13">
         <v>0.86547067559725999</v>
       </c>
-      <c r="AE13" s="9">
+      <c r="AE13">
         <v>103.71804237366</v>
       </c>
-      <c r="AF13" s="9">
+      <c r="AF13">
         <v>8</v>
       </c>
-      <c r="AG13" s="9">
+      <c r="AG13">
         <v>0.75842569873368004</v>
       </c>
     </row>
@@ -1458,22 +1457,22 @@
       <c r="V14">
         <v>0.92724374367726003</v>
       </c>
-      <c r="AA14" s="9">
+      <c r="AA14">
         <v>2661.7298126220999</v>
       </c>
-      <c r="AB14" s="9">
+      <c r="AB14">
         <v>8</v>
       </c>
-      <c r="AC14" s="9">
+      <c r="AC14">
         <v>0.84889048542110002</v>
       </c>
-      <c r="AE14" s="9">
+      <c r="AE14">
         <v>101.72772407532</v>
       </c>
-      <c r="AF14" s="9">
+      <c r="AF14">
         <v>9</v>
       </c>
-      <c r="AG14" s="9">
+      <c r="AG14">
         <v>0.86019836297556995</v>
       </c>
     </row>
@@ -1523,22 +1522,22 @@
       <c r="V15">
         <v>0.89961278476607998</v>
       </c>
-      <c r="AA15" s="9">
+      <c r="AA15">
         <v>2661.4878177643</v>
       </c>
-      <c r="AB15" s="9">
+      <c r="AB15">
         <v>9</v>
       </c>
-      <c r="AC15" s="9">
+      <c r="AC15">
         <v>0.86771171072154996</v>
       </c>
-      <c r="AE15" s="9">
+      <c r="AE15">
         <v>101.69219970703</v>
       </c>
-      <c r="AF15" s="9">
+      <c r="AF15">
         <v>10</v>
       </c>
-      <c r="AG15" s="9">
+      <c r="AG15">
         <v>0.87758417874946004</v>
       </c>
     </row>
@@ -1588,22 +1587,22 @@
       <c r="V16">
         <v>0.89666380969323001</v>
       </c>
-      <c r="AA16" s="9">
+      <c r="AA16">
         <v>2975.5327701568999</v>
       </c>
-      <c r="AB16" s="9">
+      <c r="AB16">
         <v>10</v>
       </c>
-      <c r="AC16" s="9">
+      <c r="AC16">
         <v>0.84972018591038001</v>
       </c>
-      <c r="AE16" s="9">
+      <c r="AE16">
         <v>101.90105438232</v>
       </c>
-      <c r="AF16" s="9">
+      <c r="AF16">
         <v>11</v>
       </c>
-      <c r="AG16" s="9">
+      <c r="AG16">
         <v>0.85301278149726001</v>
       </c>
     </row>
@@ -1653,22 +1652,22 @@
       <c r="V17">
         <v>0.91097098770121998</v>
       </c>
-      <c r="AA17" s="9">
+      <c r="AA17">
         <v>2586.1718654633</v>
       </c>
-      <c r="AB17" s="9">
+      <c r="AB17">
         <v>11</v>
       </c>
-      <c r="AC17" s="9">
+      <c r="AC17">
         <v>0.86790324064138002</v>
       </c>
-      <c r="AE17" s="9">
+      <c r="AE17">
         <v>101.46093368530001</v>
       </c>
-      <c r="AF17" s="9">
+      <c r="AF17">
         <v>12</v>
       </c>
-      <c r="AG17" s="9">
+      <c r="AG17">
         <v>0.81853758034294999</v>
       </c>
     </row>
@@ -1718,22 +1717,22 @@
       <c r="V18">
         <v>0.91831257442022995</v>
       </c>
-      <c r="AA18" s="9">
+      <c r="AA18">
         <v>2696.1274147034001</v>
       </c>
-      <c r="AB18" s="9">
+      <c r="AB18">
         <v>12</v>
       </c>
-      <c r="AC18" s="9">
+      <c r="AC18">
         <v>0.79289688958369997</v>
       </c>
-      <c r="AE18" s="9">
+      <c r="AE18">
         <v>101.61423683167</v>
       </c>
-      <c r="AF18" s="9">
+      <c r="AF18">
         <v>13</v>
       </c>
-      <c r="AG18" s="9">
+      <c r="AG18">
         <v>0.86074223046223997</v>
       </c>
     </row>
@@ -1783,22 +1782,22 @@
       <c r="V19">
         <v>0.90529971785437002</v>
       </c>
-      <c r="AA19" s="9">
+      <c r="AA19">
         <v>2589.9105072020998</v>
       </c>
-      <c r="AB19" s="9">
+      <c r="AB19">
         <v>13</v>
       </c>
-      <c r="AC19" s="9">
+      <c r="AC19">
         <v>0.87362348440394</v>
       </c>
-      <c r="AE19" s="9">
+      <c r="AE19">
         <v>101.59945487976</v>
       </c>
-      <c r="AF19" s="9">
+      <c r="AF19">
         <v>14</v>
       </c>
-      <c r="AG19" s="9">
+      <c r="AG19">
         <v>0.87424473514401002</v>
       </c>
     </row>
@@ -1848,22 +1847,22 @@
       <c r="V20">
         <v>0.91567316521594</v>
       </c>
-      <c r="AA20" s="9">
+      <c r="AA20">
         <v>2840.6686782837</v>
       </c>
-      <c r="AB20" s="9">
+      <c r="AB20">
         <v>14</v>
       </c>
-      <c r="AC20" s="9">
+      <c r="AC20">
         <v>0.83069312986437005</v>
       </c>
-      <c r="AE20" s="9">
+      <c r="AE20">
         <v>103.09433937073</v>
       </c>
-      <c r="AF20" s="9">
+      <c r="AF20">
         <v>15</v>
       </c>
-      <c r="AG20" s="9">
+      <c r="AG20">
         <v>0.87450848219301003</v>
       </c>
     </row>
@@ -1913,22 +1912,22 @@
       <c r="V21">
         <v>0.93141616116228998</v>
       </c>
-      <c r="AA21" s="9">
+      <c r="AA21">
         <v>2873.1908798218001</v>
       </c>
-      <c r="AB21" s="9">
+      <c r="AB21">
         <v>15</v>
       </c>
-      <c r="AC21" s="9">
+      <c r="AC21">
         <v>0.82121832036519005</v>
       </c>
-      <c r="AE21" s="9">
+      <c r="AE21">
         <v>101.33719444275</v>
       </c>
-      <c r="AF21" s="9">
+      <c r="AF21">
         <v>16</v>
       </c>
-      <c r="AG21" s="9">
+      <c r="AG21">
         <v>0.88944142323391995</v>
       </c>
     </row>
@@ -1978,22 +1977,22 @@
       <c r="V22">
         <v>0.91395767773184999</v>
       </c>
-      <c r="AA22" s="9">
+      <c r="AA22">
         <v>2939.4381046294998</v>
       </c>
-      <c r="AB22" s="9">
+      <c r="AB22">
         <v>16</v>
       </c>
-      <c r="AC22" s="9">
+      <c r="AC22">
         <v>0.87683949500873004</v>
       </c>
-      <c r="AE22" s="9">
+      <c r="AE22">
         <v>101.32479667664001</v>
       </c>
-      <c r="AF22" s="9">
+      <c r="AF22">
         <v>17</v>
       </c>
-      <c r="AG22" s="9">
+      <c r="AG22">
         <v>0.87217940706797004</v>
       </c>
     </row>
@@ -2043,22 +2042,22 @@
       <c r="V23">
         <v>0.92156318932934</v>
       </c>
-      <c r="AA23" s="9">
+      <c r="AA23">
         <v>3131.5689086913999</v>
       </c>
-      <c r="AB23" s="9">
+      <c r="AB23">
         <v>17</v>
       </c>
-      <c r="AC23" s="9">
+      <c r="AC23">
         <v>0.84883786250965998</v>
       </c>
-      <c r="AE23" s="9">
+      <c r="AE23">
         <v>101.58991813660001</v>
       </c>
-      <c r="AF23" s="9">
+      <c r="AF23">
         <v>18</v>
       </c>
-      <c r="AG23" s="9">
+      <c r="AG23">
         <v>0.86748387647888003</v>
       </c>
     </row>
@@ -2108,22 +2107,22 @@
       <c r="V24">
         <v>0.91794417928375005</v>
       </c>
-      <c r="AA24" s="9">
+      <c r="AA24">
         <v>2918.6868667602998</v>
       </c>
-      <c r="AB24" s="9">
+      <c r="AB24">
         <v>18</v>
       </c>
-      <c r="AC24" s="9">
+      <c r="AC24">
         <v>0.82086167800454002</v>
       </c>
-      <c r="AE24" s="9">
+      <c r="AE24">
         <v>102.10275650024001</v>
       </c>
-      <c r="AF24" s="9">
+      <c r="AF24">
         <v>19</v>
       </c>
-      <c r="AG24" s="9">
+      <c r="AG24">
         <v>0.86411303587332</v>
       </c>
     </row>
@@ -2173,22 +2172,22 @@
       <c r="V25">
         <v>0.90565532848612995</v>
       </c>
-      <c r="AA25" s="9">
+      <c r="AA25">
         <v>2913.2444858550998</v>
       </c>
-      <c r="AB25" s="9">
+      <c r="AB25">
         <v>19</v>
       </c>
-      <c r="AC25" s="9">
+      <c r="AC25">
         <v>0.85438472161651002</v>
       </c>
-      <c r="AE25" s="9">
+      <c r="AE25">
         <v>101.76372528076</v>
       </c>
-      <c r="AF25" s="9">
+      <c r="AF25">
         <v>20</v>
       </c>
-      <c r="AG25" s="9">
+      <c r="AG25">
         <v>0.86240255090322004</v>
       </c>
     </row>
@@ -2238,22 +2237,22 @@
       <c r="V26">
         <v>0.91375341095477003</v>
       </c>
-      <c r="AA26" s="9">
+      <c r="AA26">
         <v>2954.4155597686999</v>
       </c>
-      <c r="AB26" s="9">
+      <c r="AB26">
         <v>20</v>
       </c>
-      <c r="AC26" s="9">
+      <c r="AC26">
         <v>0.88049441059016997</v>
       </c>
-      <c r="AE26" s="9">
+      <c r="AE26">
         <v>101.32169723510999</v>
       </c>
-      <c r="AF26" s="9">
+      <c r="AF26">
         <v>21</v>
       </c>
-      <c r="AG26" s="9">
+      <c r="AG26">
         <v>0.87442283475584004</v>
       </c>
     </row>
@@ -2303,22 +2302,22 @@
       <c r="V27">
         <v>0.92512343655312002</v>
       </c>
-      <c r="AA27" s="9">
+      <c r="AA27">
         <v>2838.9434814453002</v>
       </c>
-      <c r="AB27" s="9">
+      <c r="AB27">
         <v>21</v>
       </c>
-      <c r="AC27" s="9">
+      <c r="AC27">
         <v>0.86554165913105996</v>
       </c>
-      <c r="AE27" s="9">
+      <c r="AE27">
         <v>101.55320167542</v>
       </c>
-      <c r="AF27" s="9">
+      <c r="AF27">
         <v>22</v>
       </c>
-      <c r="AG27" s="9">
+      <c r="AG27">
         <v>0.84408516087721996</v>
       </c>
     </row>
@@ -2368,22 +2367,22 @@
       <c r="V28">
         <v>0.89295034067170997</v>
       </c>
-      <c r="AA28" s="9">
+      <c r="AA28">
         <v>2754.6145915984998</v>
       </c>
-      <c r="AB28" s="9">
+      <c r="AB28">
         <v>22</v>
       </c>
-      <c r="AC28" s="9">
+      <c r="AC28">
         <v>0.86326394310817001</v>
       </c>
-      <c r="AE28" s="9">
+      <c r="AE28">
         <v>105.83782196045</v>
       </c>
-      <c r="AF28" s="9">
+      <c r="AF28">
         <v>23</v>
       </c>
-      <c r="AG28" s="9">
+      <c r="AG28">
         <v>0.86641964492144996</v>
       </c>
     </row>
@@ -2433,22 +2432,22 @@
       <c r="V29">
         <v>0.90292459141738002</v>
       </c>
-      <c r="AA29" s="9">
+      <c r="AA29">
         <v>2768.0583000183001</v>
       </c>
-      <c r="AB29" s="9">
+      <c r="AB29">
         <v>23</v>
       </c>
-      <c r="AC29" s="9">
+      <c r="AC29">
         <v>0.86531160563051002</v>
       </c>
-      <c r="AE29" s="9">
+      <c r="AE29">
         <v>101.61423683167</v>
       </c>
-      <c r="AF29" s="9">
+      <c r="AF29">
         <v>24</v>
       </c>
-      <c r="AG29" s="9">
+      <c r="AG29">
         <v>0.86299309863314999</v>
       </c>
     </row>
@@ -2498,22 +2497,22 @@
       <c r="V30">
         <v>0.92217090785110001</v>
       </c>
-      <c r="AA30" s="9">
+      <c r="AA30">
         <v>2839.7376537322998</v>
       </c>
-      <c r="AB30" s="9">
+      <c r="AB30">
         <v>24</v>
       </c>
-      <c r="AC30" s="9">
+      <c r="AC30">
         <v>0.87010714162675995</v>
       </c>
-      <c r="AE30" s="9">
+      <c r="AE30">
         <v>101.60160064697</v>
       </c>
-      <c r="AF30" s="9">
+      <c r="AF30">
         <v>25</v>
       </c>
-      <c r="AG30" s="9">
+      <c r="AG30">
         <v>0.85116253598698</v>
       </c>
     </row>
@@ -2563,22 +2562,22 @@
       <c r="V31">
         <v>0.92378429542377005</v>
       </c>
-      <c r="AA31" s="9">
+      <c r="AA31">
         <v>2840.3575420379998</v>
       </c>
-      <c r="AB31" s="9">
+      <c r="AB31">
         <v>25</v>
       </c>
-      <c r="AC31" s="9">
+      <c r="AC31">
         <v>0.85972241563384999</v>
       </c>
-      <c r="AE31" s="9">
+      <c r="AE31">
         <v>101.30453109741001</v>
       </c>
-      <c r="AF31" s="9">
+      <c r="AF31">
         <v>26</v>
       </c>
-      <c r="AG31" s="9">
+      <c r="AG31">
         <v>0.83892168679999002</v>
       </c>
     </row>
@@ -2628,22 +2627,22 @@
       <c r="V32">
         <v>0.83845038326082</v>
       </c>
-      <c r="AA32" s="9">
+      <c r="AA32">
         <v>2800.2488613128999</v>
       </c>
-      <c r="AB32" s="9">
+      <c r="AB32">
         <v>26</v>
       </c>
-      <c r="AC32" s="9">
+      <c r="AC32">
         <v>0.89295508699366</v>
       </c>
-      <c r="AE32" s="9">
+      <c r="AE32">
         <v>101.67121887207</v>
       </c>
-      <c r="AF32" s="9">
+      <c r="AF32">
         <v>27</v>
       </c>
-      <c r="AG32" s="9">
+      <c r="AG32">
         <v>0.87257493188011004</v>
       </c>
     </row>
@@ -2693,22 +2692,22 @@
       <c r="V33">
         <v>0.91478006299186998</v>
       </c>
-      <c r="AA33" s="9">
+      <c r="AA33">
         <v>2685.5707168579002</v>
       </c>
-      <c r="AB33" s="9">
+      <c r="AB33">
         <v>27</v>
       </c>
-      <c r="AC33" s="9">
+      <c r="AC33">
         <v>0.85013319176770996</v>
       </c>
-      <c r="AE33" s="9">
+      <c r="AE33">
         <v>101.65047645569</v>
       </c>
-      <c r="AF33" s="9">
+      <c r="AF33">
         <v>28</v>
       </c>
-      <c r="AG33" s="9">
+      <c r="AG33">
         <v>0.85852318802882999</v>
       </c>
     </row>
@@ -2758,22 +2757,22 @@
       <c r="V34">
         <v>0.89937106918238996</v>
       </c>
-      <c r="AA34" s="9">
+      <c r="AA34">
         <v>2866.6212558746001</v>
       </c>
-      <c r="AB34" s="9">
+      <c r="AB34">
         <v>28</v>
       </c>
-      <c r="AC34" s="9">
+      <c r="AC34">
         <v>0.83628018728438003</v>
       </c>
-      <c r="AE34" s="9">
+      <c r="AE34">
         <v>101.55606269835999</v>
       </c>
-      <c r="AF34" s="9">
+      <c r="AF34">
         <v>29</v>
       </c>
-      <c r="AG34" s="9">
+      <c r="AG34">
         <v>0.84122666313892003</v>
       </c>
     </row>
@@ -2823,22 +2822,22 @@
       <c r="V35">
         <v>0.91322623405701997</v>
       </c>
-      <c r="AA35" s="9">
+      <c r="AA35">
         <v>2759.6545219421</v>
       </c>
-      <c r="AB35" s="9">
+      <c r="AB35">
         <v>29</v>
       </c>
-      <c r="AC35" s="9">
+      <c r="AC35">
         <v>0.84789377289376999</v>
       </c>
-      <c r="AE35" s="9">
+      <c r="AE35">
         <v>101.23419761658</v>
       </c>
-      <c r="AF35" s="9">
+      <c r="AF35">
         <v>30</v>
       </c>
-      <c r="AG35" s="9">
+      <c r="AG35">
         <v>0.80707003964507995</v>
       </c>
     </row>
@@ -2888,22 +2887,22 @@
       <c r="V36">
         <v>0.91556490591203998</v>
       </c>
-      <c r="AA36" s="9">
+      <c r="AA36">
         <v>2860.2194786072</v>
       </c>
-      <c r="AB36" s="9">
+      <c r="AB36">
         <v>30</v>
       </c>
-      <c r="AC36" s="9">
+      <c r="AC36">
         <v>0.85434078788786005</v>
       </c>
-      <c r="AE36" s="9">
+      <c r="AE36">
         <v>101.45807266235001</v>
       </c>
-      <c r="AF36" s="9">
+      <c r="AF36">
         <v>31</v>
       </c>
-      <c r="AG36" s="9">
+      <c r="AG36">
         <v>0.80141064224286995</v>
       </c>
     </row>
@@ -2953,22 +2952,22 @@
       <c r="V37">
         <v>0.90386546184739003</v>
       </c>
-      <c r="AA37" s="9">
+      <c r="AA37">
         <v>3409.4717502593999</v>
       </c>
-      <c r="AB37" s="9">
+      <c r="AB37">
         <v>31</v>
       </c>
-      <c r="AC37" s="9">
+      <c r="AC37">
         <v>0.83880040553357005</v>
       </c>
-      <c r="AE37" s="9">
+      <c r="AE37">
         <v>101.39393806458</v>
       </c>
-      <c r="AF37" s="9">
+      <c r="AF37">
         <v>32</v>
       </c>
-      <c r="AG37" s="9">
+      <c r="AG37">
         <v>0.83307857618500003</v>
       </c>
     </row>
@@ -3018,22 +3017,22 @@
       <c r="V38">
         <v>0.91960307440961997</v>
       </c>
-      <c r="AA38" s="9">
+      <c r="AA38">
         <v>2883.1570148467999</v>
       </c>
-      <c r="AB38" s="9">
+      <c r="AB38">
         <v>32</v>
       </c>
-      <c r="AC38" s="9">
+      <c r="AC38">
         <v>0.82712981645721995</v>
       </c>
-      <c r="AE38" s="9">
+      <c r="AE38">
         <v>101.50861740112001</v>
       </c>
-      <c r="AF38" s="9">
+      <c r="AF38">
         <v>33</v>
       </c>
-      <c r="AG38" s="9">
+      <c r="AG38">
         <v>0.77579951721871998</v>
       </c>
     </row>
@@ -3083,22 +3082,22 @@
       <c r="V39">
         <v>0.93549629030257997</v>
       </c>
-      <c r="AA39" s="9">
+      <c r="AA39">
         <v>2831.1452865601</v>
       </c>
-      <c r="AB39" s="9">
+      <c r="AB39">
         <v>33</v>
       </c>
-      <c r="AC39" s="9">
+      <c r="AC39">
         <v>0.88179661999895997</v>
       </c>
-      <c r="AE39" s="9">
+      <c r="AE39">
         <v>101.71675682068</v>
       </c>
-      <c r="AF39" s="9">
+      <c r="AF39">
         <v>34</v>
       </c>
-      <c r="AG39" s="9">
+      <c r="AG39">
         <v>0.86901812903328002</v>
       </c>
     </row>
@@ -3148,22 +3147,22 @@
       <c r="V40">
         <v>0.85381256691648999</v>
       </c>
-      <c r="AA40" s="9">
+      <c r="AA40">
         <v>2747.5211620331002</v>
       </c>
-      <c r="AB40" s="9">
+      <c r="AB40">
         <v>34</v>
       </c>
-      <c r="AC40" s="9">
+      <c r="AC40">
         <v>0.88994941436575004</v>
       </c>
-      <c r="AE40" s="9">
+      <c r="AE40">
         <v>101.33457183838</v>
       </c>
-      <c r="AF40" s="9">
+      <c r="AF40">
         <v>35</v>
       </c>
-      <c r="AG40" s="9">
+      <c r="AG40">
         <v>0.86658755046972002</v>
       </c>
     </row>
@@ -3213,22 +3212,22 @@
       <c r="V41">
         <v>0.90648927549654001</v>
       </c>
-      <c r="AA41" s="9">
+      <c r="AA41">
         <v>3071.0675716400001</v>
       </c>
-      <c r="AB41" s="9">
+      <c r="AB41">
         <v>35</v>
       </c>
-      <c r="AC41" s="9">
+      <c r="AC41">
         <v>0.86492399211825999</v>
       </c>
-      <c r="AE41" s="9">
+      <c r="AE41">
         <v>101.56655311583999</v>
       </c>
-      <c r="AF41" s="9">
+      <c r="AF41">
         <v>36</v>
       </c>
-      <c r="AG41" s="9">
+      <c r="AG41">
         <v>0.86653848085464003</v>
       </c>
     </row>
@@ -3278,22 +3277,22 @@
       <c r="V42">
         <v>0.92656902916953998</v>
       </c>
-      <c r="AA42" s="9">
+      <c r="AA42">
         <v>2885.3526115416998</v>
       </c>
-      <c r="AB42" s="9">
+      <c r="AB42">
         <v>36</v>
       </c>
-      <c r="AC42" s="9">
+      <c r="AC42">
         <v>0.8515794997824</v>
       </c>
-      <c r="AE42" s="9">
+      <c r="AE42">
         <v>101.5043258667</v>
       </c>
-      <c r="AF42" s="9">
+      <c r="AF42">
         <v>37</v>
       </c>
-      <c r="AG42" s="9">
+      <c r="AG42">
         <v>0.85157960442345004</v>
       </c>
     </row>
@@ -3343,22 +3342,22 @@
       <c r="V43">
         <v>0.89216916836962001</v>
       </c>
-      <c r="AA43" s="9">
+      <c r="AA43">
         <v>2546.2486743927002</v>
       </c>
-      <c r="AB43" s="9">
+      <c r="AB43">
         <v>37</v>
       </c>
-      <c r="AC43" s="9">
+      <c r="AC43">
         <v>0.80619299325648996</v>
       </c>
-      <c r="AE43" s="9">
+      <c r="AE43">
         <v>101.46570205688</v>
       </c>
-      <c r="AF43" s="9">
+      <c r="AF43">
         <v>38</v>
       </c>
-      <c r="AG43" s="9">
+      <c r="AG43">
         <v>0.88210637781553003</v>
       </c>
     </row>
@@ -3408,22 +3407,22 @@
       <c r="V44">
         <v>0.90177573670111</v>
       </c>
-      <c r="AA44" s="9">
+      <c r="AA44">
         <v>2733.6301803588999</v>
       </c>
-      <c r="AB44" s="9">
+      <c r="AB44">
         <v>38</v>
       </c>
-      <c r="AC44" s="9">
+      <c r="AC44">
         <v>0.89624464024879003</v>
       </c>
-      <c r="AE44" s="9">
+      <c r="AE44">
         <v>101.4575958252</v>
       </c>
-      <c r="AF44" s="9">
+      <c r="AF44">
         <v>39</v>
       </c>
-      <c r="AG44" s="9">
+      <c r="AG44">
         <v>0.84702895971025005</v>
       </c>
     </row>
@@ -3473,22 +3472,22 @@
       <c r="V45">
         <v>0.90299634835676001</v>
       </c>
-      <c r="AA45" s="9">
+      <c r="AA45">
         <v>2982.6829433440998</v>
       </c>
-      <c r="AB45" s="9">
+      <c r="AB45">
         <v>39</v>
       </c>
-      <c r="AC45" s="9">
+      <c r="AC45">
         <v>0.82500900664854004</v>
       </c>
-      <c r="AE45" s="9">
+      <c r="AE45">
         <v>101.53555870056</v>
       </c>
-      <c r="AF45" s="9">
+      <c r="AF45">
         <v>40</v>
       </c>
-      <c r="AG45" s="9">
+      <c r="AG45">
         <v>0.87588628935271995</v>
       </c>
     </row>
@@ -3538,22 +3537,22 @@
       <c r="V46">
         <v>0.90279686416166005</v>
       </c>
-      <c r="AA46" s="9">
+      <c r="AA46">
         <v>3032.5210094452</v>
       </c>
-      <c r="AB46" s="9">
+      <c r="AB46">
         <v>40</v>
       </c>
-      <c r="AC46" s="9">
+      <c r="AC46">
         <v>0.85239737817350003</v>
       </c>
-      <c r="AE46" s="9">
+      <c r="AE46">
         <v>105.4675579071</v>
       </c>
-      <c r="AF46" s="9">
+      <c r="AF46">
         <v>41</v>
       </c>
-      <c r="AG46" s="9">
+      <c r="AG46">
         <v>0.85803691366364998</v>
       </c>
     </row>
@@ -3603,22 +3602,22 @@
       <c r="V47">
         <v>0.88450018243065998</v>
       </c>
-      <c r="AA47" s="9">
+      <c r="AA47">
         <v>3141.1225795746</v>
       </c>
-      <c r="AB47" s="9">
+      <c r="AB47">
         <v>41</v>
       </c>
-      <c r="AC47" s="9">
+      <c r="AC47">
         <v>0.80141481702791995</v>
       </c>
-      <c r="AE47" s="9">
+      <c r="AE47">
         <v>101.50551795958999</v>
       </c>
-      <c r="AF47" s="9">
+      <c r="AF47">
         <v>42</v>
       </c>
-      <c r="AG47" s="9">
+      <c r="AG47">
         <v>0.85073544369853005</v>
       </c>
     </row>
@@ -3668,22 +3667,22 @@
       <c r="V48">
         <v>0.86992349432104998</v>
       </c>
-      <c r="AA48" s="9">
+      <c r="AA48">
         <v>3083.6257934569999</v>
       </c>
-      <c r="AB48" s="9">
+      <c r="AB48">
         <v>42</v>
       </c>
-      <c r="AC48" s="9">
+      <c r="AC48">
         <v>0.86580726698262001</v>
       </c>
-      <c r="AE48" s="9">
+      <c r="AE48">
         <v>99.531412124634002</v>
       </c>
-      <c r="AF48" s="9">
+      <c r="AF48">
         <v>43</v>
       </c>
-      <c r="AG48" s="9">
+      <c r="AG48">
         <v>0.86478596083744996</v>
       </c>
     </row>
@@ -3733,22 +3732,22 @@
       <c r="V49">
         <v>0.92135362989744995</v>
       </c>
-      <c r="AA49" s="9">
+      <c r="AA49">
         <v>3019.2501544952001</v>
       </c>
-      <c r="AB49" s="9">
+      <c r="AB49">
         <v>43</v>
       </c>
-      <c r="AC49" s="9">
+      <c r="AC49">
         <v>0.88283651283847997</v>
       </c>
-      <c r="AE49" s="9">
+      <c r="AE49">
         <v>101.52196884155001</v>
       </c>
-      <c r="AF49" s="9">
+      <c r="AF49">
         <v>44</v>
       </c>
-      <c r="AG49" s="9">
+      <c r="AG49">
         <v>0.80751921933887005</v>
       </c>
     </row>
@@ -3798,22 +3797,22 @@
       <c r="V50">
         <v>0.92735212662802002</v>
       </c>
-      <c r="AA50" s="9">
+      <c r="AA50">
         <v>3042.7575111389001</v>
       </c>
-      <c r="AB50" s="9">
+      <c r="AB50">
         <v>44</v>
       </c>
-      <c r="AC50" s="9">
+      <c r="AC50">
         <v>0.89050426869926003</v>
       </c>
-      <c r="AE50" s="9">
+      <c r="AE50">
         <v>101.22466087341</v>
       </c>
-      <c r="AF50" s="9">
+      <c r="AF50">
         <v>45</v>
       </c>
-      <c r="AG50" s="9">
+      <c r="AG50">
         <v>0.85073430551245999</v>
       </c>
     </row>
@@ -3863,22 +3862,22 @@
       <c r="V51">
         <v>0.92592415383585003</v>
       </c>
-      <c r="AA51" s="9">
+      <c r="AA51">
         <v>3168.6284542083999</v>
       </c>
-      <c r="AB51" s="9">
+      <c r="AB51">
         <v>45</v>
       </c>
-      <c r="AC51" s="9">
+      <c r="AC51">
         <v>0.83089536582384005</v>
       </c>
-      <c r="AE51" s="9">
+      <c r="AE51">
         <v>102.04887390137</v>
       </c>
-      <c r="AF51" s="9">
+      <c r="AF51">
         <v>46</v>
       </c>
-      <c r="AG51" s="9">
+      <c r="AG51">
         <v>0.84946329030794998</v>
       </c>
     </row>
@@ -3928,22 +3927,22 @@
       <c r="V52">
         <v>0.92405995219095005</v>
       </c>
-      <c r="AA52" s="9">
+      <c r="AA52">
         <v>2918.3607101440002</v>
       </c>
-      <c r="AB52" s="9">
+      <c r="AB52">
         <v>46</v>
       </c>
-      <c r="AC52" s="9">
+      <c r="AC52">
         <v>0.87551227184055003</v>
       </c>
-      <c r="AE52" s="9">
+      <c r="AE52">
         <v>101.77993774414</v>
       </c>
-      <c r="AF52" s="9">
+      <c r="AF52">
         <v>47</v>
       </c>
-      <c r="AG52" s="9">
+      <c r="AG52">
         <v>0.79688340878153996</v>
       </c>
     </row>
@@ -3993,22 +3992,22 @@
       <c r="V53">
         <v>0.88629348529134999</v>
       </c>
-      <c r="AA53" s="9">
+      <c r="AA53">
         <v>2773.5455036162998</v>
       </c>
-      <c r="AB53" s="9">
+      <c r="AB53">
         <v>47</v>
       </c>
-      <c r="AC53" s="9">
+      <c r="AC53">
         <v>0.81674717964593002</v>
       </c>
-      <c r="AE53" s="9">
+      <c r="AE53">
         <v>101.72438621521</v>
       </c>
-      <c r="AF53" s="9">
+      <c r="AF53">
         <v>48</v>
       </c>
-      <c r="AG53" s="9">
+      <c r="AG53">
         <v>0.86230631398643998</v>
       </c>
     </row>
@@ -4058,22 +4057,22 @@
       <c r="V54">
         <v>0.93198923629607999</v>
       </c>
-      <c r="AA54" s="9">
+      <c r="AA54">
         <v>2691.1709308623999</v>
       </c>
-      <c r="AB54" s="9">
+      <c r="AB54">
         <v>48</v>
       </c>
-      <c r="AC54" s="9">
+      <c r="AC54">
         <v>0.87007058214078004</v>
       </c>
-      <c r="AE54" s="9">
+      <c r="AE54">
         <v>101.57108306885</v>
       </c>
-      <c r="AF54" s="9">
+      <c r="AF54">
         <v>49</v>
       </c>
-      <c r="AG54" s="9">
+      <c r="AG54">
         <v>0.86511931033593004</v>
       </c>
     </row>
@@ -4123,22 +4122,22 @@
       <c r="V55">
         <v>0.92017103342050999</v>
       </c>
-      <c r="AA55" s="9">
+      <c r="AA55">
         <v>2664.1442775726</v>
       </c>
-      <c r="AB55" s="9">
+      <c r="AB55">
         <v>49</v>
       </c>
-      <c r="AC55" s="9">
+      <c r="AC55">
         <v>0.83421700515078001</v>
       </c>
-      <c r="AE55" s="9">
+      <c r="AE55">
         <v>101.39274597168</v>
       </c>
-      <c r="AF55" s="9">
+      <c r="AF55">
         <v>50</v>
       </c>
-      <c r="AG55" s="9">
+      <c r="AG55">
         <v>0.85415678368120995</v>
       </c>
     </row>
@@ -4188,22 +4187,22 @@
       <c r="V56">
         <v>0.90959947545374997</v>
       </c>
-      <c r="AA56" s="9">
+      <c r="AA56">
         <v>2761.8713378906</v>
       </c>
-      <c r="AB56" s="9">
+      <c r="AB56">
         <v>50</v>
       </c>
-      <c r="AC56" s="9">
+      <c r="AC56">
         <v>0.85975037003302002</v>
       </c>
-      <c r="AE56" s="9">
+      <c r="AE56">
         <v>102.03051567078001</v>
       </c>
-      <c r="AF56" s="9">
+      <c r="AF56">
         <v>51</v>
       </c>
-      <c r="AG56" s="9">
+      <c r="AG56">
         <v>0.88743087330324999</v>
       </c>
     </row>
@@ -4253,22 +4252,22 @@
       <c r="V57">
         <v>0.90001012555690996</v>
       </c>
-      <c r="AA57" s="9">
+      <c r="AA57">
         <v>2909.0342521666998</v>
       </c>
-      <c r="AB57" s="9">
+      <c r="AB57">
         <v>51</v>
       </c>
-      <c r="AC57" s="9">
+      <c r="AC57">
         <v>0.84410040412089005</v>
       </c>
-      <c r="AE57" s="9">
+      <c r="AE57">
         <v>101.40466690063</v>
       </c>
-      <c r="AF57" s="9">
+      <c r="AF57">
         <v>52</v>
       </c>
-      <c r="AG57" s="9">
+      <c r="AG57">
         <v>0.85439587898359004</v>
       </c>
     </row>
@@ -4318,22 +4317,22 @@
       <c r="V58">
         <v>0.93037776827141005</v>
       </c>
-      <c r="AA58" s="9">
+      <c r="AA58">
         <v>2995.4619407654</v>
       </c>
-      <c r="AB58" s="9">
+      <c r="AB58">
         <v>52</v>
       </c>
-      <c r="AC58" s="9">
+      <c r="AC58">
         <v>0.85392294248239997</v>
       </c>
-      <c r="AE58" s="9">
+      <c r="AE58">
         <v>101.75538063049</v>
       </c>
-      <c r="AF58" s="9">
+      <c r="AF58">
         <v>53</v>
       </c>
-      <c r="AG58" s="9">
+      <c r="AG58">
         <v>0.85085139795540998</v>
       </c>
     </row>
@@ -4383,22 +4382,22 @@
       <c r="V59">
         <v>0.90249035742996997</v>
       </c>
-      <c r="AA59" s="9">
+      <c r="AA59">
         <v>2821.8157291411999</v>
       </c>
-      <c r="AB59" s="9">
+      <c r="AB59">
         <v>53</v>
       </c>
-      <c r="AC59" s="9">
+      <c r="AC59">
         <v>0.86508496878860996</v>
       </c>
-      <c r="AE59" s="9">
+      <c r="AE59">
         <v>101.54604911804</v>
       </c>
-      <c r="AF59" s="9">
+      <c r="AF59">
         <v>54</v>
       </c>
-      <c r="AG59" s="9">
+      <c r="AG59">
         <v>0.88631718744235999</v>
       </c>
     </row>
@@ -4448,22 +4447,22 @@
       <c r="V60">
         <v>0.91551357294835001</v>
       </c>
-      <c r="AA60" s="9">
+      <c r="AA60">
         <v>2767.3931121825999</v>
       </c>
-      <c r="AB60" s="9">
+      <c r="AB60">
         <v>54</v>
       </c>
-      <c r="AC60" s="9">
+      <c r="AC60">
         <v>0.84735436753993998</v>
       </c>
-      <c r="AE60" s="9">
+      <c r="AE60">
         <v>101.36985778809</v>
       </c>
-      <c r="AF60" s="9">
+      <c r="AF60">
         <v>55</v>
       </c>
-      <c r="AG60" s="9">
+      <c r="AG60">
         <v>0.83518586431071995</v>
       </c>
     </row>
@@ -4513,22 +4512,22 @@
       <c r="V61">
         <v>0.93911348860695998</v>
       </c>
-      <c r="AA61" s="9">
+      <c r="AA61">
         <v>3100.4803180694998</v>
       </c>
-      <c r="AB61" s="9">
+      <c r="AB61">
         <v>55</v>
       </c>
-      <c r="AC61" s="9">
+      <c r="AC61">
         <v>0.89009483124669997</v>
       </c>
-      <c r="AE61" s="9">
+      <c r="AE61">
         <v>101.39346122742</v>
       </c>
-      <c r="AF61" s="9">
+      <c r="AF61">
         <v>56</v>
       </c>
-      <c r="AG61" s="9">
+      <c r="AG61">
         <v>0.87315336695343004</v>
       </c>
     </row>
@@ -4578,22 +4577,22 @@
       <c r="V62">
         <v>0.90336239622878001</v>
       </c>
-      <c r="AA62" s="9">
+      <c r="AA62">
         <v>2925.2233505249001</v>
       </c>
-      <c r="AB62" s="9">
+      <c r="AB62">
         <v>56</v>
       </c>
-      <c r="AC62" s="9">
+      <c r="AC62">
         <v>0.83591555021546005</v>
       </c>
-      <c r="AE62" s="9">
+      <c r="AE62">
         <v>101.87220573425</v>
       </c>
-      <c r="AF62" s="9">
+      <c r="AF62">
         <v>57</v>
       </c>
-      <c r="AG62" s="9">
+      <c r="AG62">
         <v>0.84608756878948999</v>
       </c>
     </row>
@@ -4643,22 +4642,22 @@
       <c r="V63">
         <v>0.92335763267352999</v>
       </c>
-      <c r="AA63" s="9">
+      <c r="AA63">
         <v>2808.3918094635001</v>
       </c>
-      <c r="AB63" s="9">
+      <c r="AB63">
         <v>57</v>
       </c>
-      <c r="AC63" s="9">
+      <c r="AC63">
         <v>0.87457006358667</v>
       </c>
-      <c r="AE63" s="9">
+      <c r="AE63">
         <v>101.1426448822</v>
       </c>
-      <c r="AF63" s="9">
+      <c r="AF63">
         <v>58</v>
       </c>
-      <c r="AG63" s="9">
+      <c r="AG63">
         <v>0.85047121354235999</v>
       </c>
     </row>
@@ -4708,22 +4707,22 @@
       <c r="V64">
         <v>0.90007053023372996</v>
       </c>
-      <c r="AA64" s="9">
+      <c r="AA64">
         <v>2727.751493454</v>
       </c>
-      <c r="AB64" s="9">
+      <c r="AB64">
         <v>58</v>
       </c>
-      <c r="AC64" s="9">
+      <c r="AC64">
         <v>0.84590969910072</v>
       </c>
-      <c r="AE64" s="9">
+      <c r="AE64">
         <v>101.50861740112001</v>
       </c>
-      <c r="AF64" s="9">
+      <c r="AF64">
         <v>59</v>
       </c>
-      <c r="AG64" s="9">
+      <c r="AG64">
         <v>0.78605624425350995</v>
       </c>
     </row>
@@ -4773,22 +4772,22 @@
       <c r="V65">
         <v>0.91170859045079999</v>
       </c>
-      <c r="AA65" s="9">
+      <c r="AA65">
         <v>2816.3638114928999</v>
       </c>
-      <c r="AB65" s="9">
+      <c r="AB65">
         <v>59</v>
       </c>
-      <c r="AC65" s="9">
+      <c r="AC65">
         <v>0.85918008763424003</v>
       </c>
-      <c r="AE65" s="9">
+      <c r="AE65">
         <v>101.36318206787</v>
       </c>
-      <c r="AF65" s="9">
+      <c r="AF65">
         <v>60</v>
       </c>
-      <c r="AG65" s="9">
+      <c r="AG65">
         <v>0.54532234349678999</v>
       </c>
     </row>
@@ -4838,22 +4837,22 @@
       <c r="V66">
         <v>0.91062429432985004</v>
       </c>
-      <c r="AA66" s="9">
+      <c r="AA66">
         <v>2812.9999637604001</v>
       </c>
-      <c r="AB66" s="9">
+      <c r="AB66">
         <v>60</v>
       </c>
-      <c r="AC66" s="9">
+      <c r="AC66">
         <v>0.80353606451767001</v>
       </c>
-      <c r="AE66" s="9">
+      <c r="AE66">
         <v>102.24318504333</v>
       </c>
-      <c r="AF66" s="9">
+      <c r="AF66">
         <v>61</v>
       </c>
-      <c r="AG66" s="9">
+      <c r="AG66">
         <v>0.83597169682512995</v>
       </c>
     </row>
@@ -4903,22 +4902,22 @@
       <c r="V67">
         <v>0.87914196415857004</v>
       </c>
-      <c r="AA67" s="9">
+      <c r="AA67">
         <v>2919.2216396332001</v>
       </c>
-      <c r="AB67" s="9">
+      <c r="AB67">
         <v>61</v>
       </c>
-      <c r="AC67" s="9">
+      <c r="AC67">
         <v>0.51371859173708001</v>
       </c>
-      <c r="AE67" s="9">
+      <c r="AE67">
         <v>101.60660743712999</v>
       </c>
-      <c r="AF67" s="9">
+      <c r="AF67">
         <v>62</v>
       </c>
-      <c r="AG67" s="9">
+      <c r="AG67">
         <v>0.85039141552798003</v>
       </c>
     </row>
@@ -4968,22 +4967,22 @@
       <c r="V68">
         <v>0.92995273208546003</v>
       </c>
-      <c r="AA68" s="9">
+      <c r="AA68">
         <v>2985.7130050658998</v>
       </c>
-      <c r="AB68" s="9">
+      <c r="AB68">
         <v>62</v>
       </c>
-      <c r="AC68" s="9">
+      <c r="AC68">
         <v>0.86084610960153995</v>
       </c>
-      <c r="AE68" s="9">
+      <c r="AE68">
         <v>101.78470611572</v>
       </c>
-      <c r="AF68" s="9">
+      <c r="AF68">
         <v>63</v>
       </c>
-      <c r="AG68" s="9">
+      <c r="AG68">
         <v>0.85547555245967999</v>
       </c>
     </row>
@@ -5033,22 +5032,22 @@
       <c r="V69">
         <v>0.91618264482585998</v>
       </c>
-      <c r="AA69" s="9">
+      <c r="AA69">
         <v>2854.6442985535</v>
       </c>
-      <c r="AB69" s="9">
+      <c r="AB69">
         <v>63</v>
       </c>
-      <c r="AC69" s="9">
+      <c r="AC69">
         <v>0.79796540200511001</v>
       </c>
-      <c r="AE69" s="9">
+      <c r="AE69">
         <v>102.08582878113</v>
       </c>
-      <c r="AF69" s="9">
+      <c r="AF69">
         <v>64</v>
       </c>
-      <c r="AG69" s="9">
+      <c r="AG69">
         <v>0.83082887136085004</v>
       </c>
     </row>
@@ -5098,22 +5097,22 @@
       <c r="V70">
         <v>0.91536785994533998</v>
       </c>
-      <c r="AA70" s="9">
+      <c r="AA70">
         <v>3079.5779228209999</v>
       </c>
-      <c r="AB70" s="9">
+      <c r="AB70">
         <v>64</v>
       </c>
-      <c r="AC70" s="9">
+      <c r="AC70">
         <v>0.86809209176345004</v>
       </c>
-      <c r="AE70" s="9">
+      <c r="AE70">
         <v>101.58300399780001</v>
       </c>
-      <c r="AF70" s="9">
+      <c r="AF70">
         <v>65</v>
       </c>
-      <c r="AG70" s="9">
+      <c r="AG70">
         <v>0.85474456568704005</v>
       </c>
     </row>
@@ -5163,22 +5162,22 @@
       <c r="V71">
         <v>0.92537977320585996</v>
       </c>
-      <c r="AA71" s="9">
+      <c r="AA71">
         <v>3028.5627841948999</v>
       </c>
-      <c r="AB71" s="9">
+      <c r="AB71">
         <v>65</v>
       </c>
-      <c r="AC71" s="9">
+      <c r="AC71">
         <v>0.86021556848008995</v>
       </c>
-      <c r="AE71" s="9">
+      <c r="AE71">
         <v>101.21154785156</v>
       </c>
-      <c r="AF71" s="9">
+      <c r="AF71">
         <v>66</v>
       </c>
-      <c r="AG71" s="9">
+      <c r="AG71">
         <v>0.86222527603614996</v>
       </c>
     </row>
@@ -5228,22 +5227,22 @@
       <c r="V72">
         <v>0.89761131157443996</v>
       </c>
-      <c r="AA72" s="9">
+      <c r="AA72">
         <v>3083.8050842285002</v>
       </c>
-      <c r="AB72" s="9">
+      <c r="AB72">
         <v>66</v>
       </c>
-      <c r="AC72" s="9">
+      <c r="AC72">
         <v>0.87222903366732996</v>
       </c>
-      <c r="AE72" s="9">
+      <c r="AE72">
         <v>101.81498527527</v>
       </c>
-      <c r="AF72" s="9">
+      <c r="AF72">
         <v>67</v>
       </c>
-      <c r="AG72" s="9">
+      <c r="AG72">
         <v>0.87745890928611003</v>
       </c>
     </row>
@@ -5293,22 +5292,22 @@
       <c r="V73">
         <v>0.93327641477519996</v>
       </c>
-      <c r="AA73" s="9">
+      <c r="AA73">
         <v>3230.3395271301001</v>
       </c>
-      <c r="AB73" s="9">
+      <c r="AB73">
         <v>67</v>
       </c>
-      <c r="AC73" s="9">
+      <c r="AC73">
         <v>0.87843826685712001</v>
       </c>
-      <c r="AE73" s="9">
+      <c r="AE73">
         <v>101.35817527771</v>
       </c>
-      <c r="AF73" s="9">
+      <c r="AF73">
         <v>68</v>
       </c>
-      <c r="AG73" s="9">
+      <c r="AG73">
         <v>0.86369415727495003</v>
       </c>
     </row>
@@ -5358,22 +5357,22 @@
       <c r="V74">
         <v>0.84873148280237998</v>
       </c>
-      <c r="AA74" s="9">
+      <c r="AA74">
         <v>3033.894777298</v>
       </c>
-      <c r="AB74" s="9">
+      <c r="AB74">
         <v>68</v>
       </c>
-      <c r="AC74" s="9">
+      <c r="AC74">
         <v>0.83834472462619003</v>
       </c>
-      <c r="AE74" s="9">
+      <c r="AE74">
         <v>101.57418251038</v>
       </c>
-      <c r="AF74" s="9">
+      <c r="AF74">
         <v>69</v>
       </c>
-      <c r="AG74" s="9">
+      <c r="AG74">
         <v>0.87346628595882003</v>
       </c>
     </row>
@@ -5423,22 +5422,22 @@
       <c r="V75">
         <v>0.93636480834240998</v>
       </c>
-      <c r="AA75" s="9">
+      <c r="AA75">
         <v>3038.6204719542998</v>
       </c>
-      <c r="AB75" s="9">
+      <c r="AB75">
         <v>69</v>
       </c>
-      <c r="AC75" s="9">
+      <c r="AC75">
         <v>0.80334019121384004</v>
       </c>
-      <c r="AE75" s="9">
+      <c r="AE75">
         <v>101.35746002197</v>
       </c>
-      <c r="AF75" s="9">
+      <c r="AF75">
         <v>70</v>
       </c>
-      <c r="AG75" s="9">
+      <c r="AG75">
         <v>0.85625438319320002</v>
       </c>
     </row>
@@ -5488,22 +5487,22 @@
       <c r="V76">
         <v>0.91260542720938997</v>
       </c>
-      <c r="AA76" s="9">
+      <c r="AA76">
         <v>3162.8456115723002</v>
       </c>
-      <c r="AB76" s="9">
+      <c r="AB76">
         <v>70</v>
       </c>
-      <c r="AC76" s="9">
+      <c r="AC76">
         <v>0.85781039794302005</v>
       </c>
-      <c r="AE76" s="9">
+      <c r="AE76">
         <v>101.27687454223999</v>
       </c>
-      <c r="AF76" s="9">
+      <c r="AF76">
         <v>71</v>
       </c>
-      <c r="AG76" s="9">
+      <c r="AG76">
         <v>0.85841093464351004</v>
       </c>
     </row>
@@ -5553,22 +5552,22 @@
       <c r="V77">
         <v>0.92486829181176999</v>
       </c>
-      <c r="AA77" s="9">
+      <c r="AA77">
         <v>2843.1003093719</v>
       </c>
-      <c r="AB77" s="9">
+      <c r="AB77">
         <v>71</v>
       </c>
-      <c r="AC77" s="9">
+      <c r="AC77">
         <v>0.85809986842527997</v>
       </c>
-      <c r="AE77" s="9">
+      <c r="AE77">
         <v>101.4518737793</v>
       </c>
-      <c r="AF77" s="9">
+      <c r="AF77">
         <v>72</v>
       </c>
-      <c r="AG77" s="9">
+      <c r="AG77">
         <v>0.82990196078431</v>
       </c>
     </row>
@@ -5618,22 +5617,22 @@
       <c r="V78">
         <v>0.92864822006907</v>
       </c>
-      <c r="AA78" s="9">
+      <c r="AA78">
         <v>2830.2469253539998</v>
       </c>
-      <c r="AB78" s="9">
+      <c r="AB78">
         <v>72</v>
       </c>
-      <c r="AC78" s="9">
+      <c r="AC78">
         <v>0.85391015996806996</v>
       </c>
-      <c r="AE78" s="9">
+      <c r="AE78">
         <v>102.37073898315001</v>
       </c>
-      <c r="AF78" s="9">
+      <c r="AF78">
         <v>73</v>
       </c>
-      <c r="AG78" s="9">
+      <c r="AG78">
         <v>0.85919819538943998</v>
       </c>
     </row>
@@ -5683,22 +5682,22 @@
       <c r="V79">
         <v>0.93419152336754996</v>
       </c>
-      <c r="AA79" s="9">
+      <c r="AA79">
         <v>2898.4766006469999</v>
       </c>
-      <c r="AB79" s="9">
+      <c r="AB79">
         <v>73</v>
       </c>
-      <c r="AC79" s="9">
+      <c r="AC79">
         <v>0.84562096779050999</v>
       </c>
-      <c r="AE79" s="9">
+      <c r="AE79">
         <v>101.72438621521</v>
       </c>
-      <c r="AF79" s="9">
+      <c r="AF79">
         <v>74</v>
       </c>
-      <c r="AG79" s="9">
+      <c r="AG79">
         <v>0.84253486340772998</v>
       </c>
     </row>
@@ -5748,13 +5747,13 @@
       <c r="V80" t="s">
         <v>12</v>
       </c>
-      <c r="AA80" s="9">
+      <c r="AA80">
         <v>2618.4508800507001</v>
       </c>
-      <c r="AB80" s="9">
+      <c r="AB80">
         <v>74</v>
       </c>
-      <c r="AC80" s="9">
+      <c r="AC80">
         <v>0.80679215498347001</v>
       </c>
       <c r="AE80">
@@ -5810,6 +5809,42 @@
       <c r="AC81">
         <f>AVERAGE(AC6:AC80)</f>
         <v>0.84709552398501553</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29">
+      <c r="O83">
+        <f>STDEVA(O4:O78)</f>
+        <v>3456.7580280154807</v>
+      </c>
+      <c r="Q83">
+        <f>STDEVA(Q4:Q78)</f>
+        <v>0.10703762020379891</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29">
+      <c r="A84">
+        <f>STDEVA(A5:A79)</f>
+        <v>1209.2555626440048</v>
+      </c>
+      <c r="C84">
+        <f>STDEVA(C5:C79)</f>
+        <v>0.1063540599391375</v>
+      </c>
+      <c r="F84">
+        <f>STDEVA(F5:F79)</f>
+        <v>54.634336022721079</v>
+      </c>
+      <c r="H84">
+        <f>STDEVA(H5:H79)</f>
+        <v>0.1065076049092654</v>
+      </c>
+      <c r="T84">
+        <f>STDEVA(T5:T79)</f>
+        <v>53.992509630076263</v>
+      </c>
+      <c r="V84">
+        <f>STDEVA(V5:V79)</f>
+        <v>1.9523845313406989E-2</v>
       </c>
     </row>
     <row r="86" spans="1:29">
